--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SprintUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="700" documentId="13_ncr:1_{0B453FD3-798C-44F1-AE68-DB3CC695CE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12890262-6F7D-48AA-8592-3C345654A10D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F442ABD6-F405-47C0-B82C-608641BE0EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25965" windowHeight="14745" xr2:uid="{6DE6BE46-6D40-408E-8663-EDE3F977B8C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DE6BE46-6D40-408E-8663-EDE3F977B8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="100">
   <si>
     <t>ゲーム開発コスト表</t>
     <rPh sb="3" eb="5">
@@ -430,12 +430,6 @@
     <t>チェックポイントのエフェクト</t>
   </si>
   <si>
-    <t>登った距離</t>
-  </si>
-  <si>
-    <t>作業に余裕ができた人</t>
-  </si>
-  <si>
     <t>　　　</t>
   </si>
   <si>
@@ -482,6 +476,13 @@
     <t>提出</t>
     <rPh sb="0" eb="2">
       <t>テイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登った距離計測</t>
+    <rPh sb="5" eb="7">
+      <t>ケイソク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -490,7 +491,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,7 +511,8 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="游ゴシック"/>
-      <charset val="1"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1401,8 +1403,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195CECDA-BF26-46FD-803C-75E03120C647}">
-  <dimension ref="A2:M68"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A2:M61"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="13.75" customWidth="1"/>
@@ -1415,12 +1417,12 @@
     <col min="12" max="12" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="15.75">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B3" s="10" t="s">
         <v>1</v>
       </c>
@@ -1453,7 +1455,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B4" s="13" t="s">
         <v>10</v>
       </c>
@@ -1484,7 +1486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B5" s="13"/>
       <c r="C5" s="8" t="s">
         <v>15</v>
@@ -1513,7 +1515,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B6" s="13"/>
       <c r="C6" s="8" t="s">
         <v>17</v>
@@ -1542,7 +1544,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B7" s="13"/>
       <c r="C7" s="9" t="s">
         <v>19</v>
@@ -1564,7 +1566,7 @@
       </c>
       <c r="I7" s="15"/>
     </row>
-    <row r="8" spans="1:12" ht="15.75">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B8" s="13"/>
       <c r="C8" s="9" t="s">
         <v>21</v>
@@ -1588,7 +1590,7 @@
       </c>
       <c r="L8" s="27"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B9" s="13"/>
       <c r="C9" s="9" t="s">
         <v>23</v>
@@ -1614,7 +1616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B10" s="13"/>
       <c r="C10" s="8" t="s">
         <v>24</v>
@@ -1642,7 +1644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B11" s="13"/>
       <c r="C11" s="8" t="s">
         <v>25</v>
@@ -1671,7 +1673,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B12" s="13"/>
       <c r="C12" s="8" t="s">
         <v>26</v>
@@ -1693,7 +1695,7 @@
       </c>
       <c r="I12" s="14"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B13" s="13"/>
       <c r="C13" s="8" t="s">
         <v>29</v>
@@ -1715,7 +1717,7 @@
       </c>
       <c r="I13" s="14"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B14" s="13"/>
       <c r="C14" s="8" t="s">
         <v>31</v>
@@ -1737,7 +1739,7 @@
       </c>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B15" s="13"/>
       <c r="C15" s="8" t="s">
         <v>32</v>
@@ -1759,7 +1761,7 @@
       </c>
       <c r="I15" s="14"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B16" s="13"/>
       <c r="C16" s="8" t="s">
         <v>33</v>
@@ -1781,7 +1783,7 @@
       </c>
       <c r="I16" s="14"/>
     </row>
-    <row r="17" spans="2:13" ht="15.75">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B17" s="16" t="s">
         <v>35</v>
       </c>
@@ -1805,7 +1807,7 @@
       </c>
       <c r="I17" s="14"/>
     </row>
-    <row r="18" spans="2:13" ht="15.75">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B18" s="16"/>
       <c r="C18" s="8" t="s">
         <v>38</v>
@@ -1827,7 +1829,7 @@
       </c>
       <c r="I18" s="14"/>
     </row>
-    <row r="19" spans="2:13" ht="15.75">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B19" s="16"/>
       <c r="C19" s="8" t="s">
         <v>39</v>
@@ -1856,7 +1858,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="15.75">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B20" s="17" t="s">
         <v>41</v>
       </c>
@@ -1881,7 +1883,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="2:13" ht="15.75">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B21" s="17"/>
       <c r="C21" s="8" t="s">
         <v>24</v>
@@ -1903,7 +1905,7 @@
       </c>
       <c r="I21" s="14"/>
     </row>
-    <row r="22" spans="2:13" ht="15.75">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B22" s="17"/>
       <c r="C22" s="8" t="s">
         <v>44</v>
@@ -1926,7 +1928,7 @@
       <c r="I22" s="14"/>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" spans="2:13" ht="15.75">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B23" s="17"/>
       <c r="C23" s="8" t="s">
         <v>45</v>
@@ -1948,7 +1950,7 @@
       </c>
       <c r="I23" s="14"/>
     </row>
-    <row r="24" spans="2:13" ht="15.75">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B24" s="17"/>
       <c r="C24" s="8" t="s">
         <v>47</v>
@@ -1970,7 +1972,7 @@
       </c>
       <c r="I24" s="14"/>
     </row>
-    <row r="25" spans="2:13" ht="15.75">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B25" s="17"/>
       <c r="C25" s="8" t="s">
         <v>48</v>
@@ -1992,7 +1994,7 @@
       </c>
       <c r="I25" s="14"/>
     </row>
-    <row r="26" spans="2:13" ht="15.75">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B26" s="17"/>
       <c r="C26" s="8" t="s">
         <v>50</v>
@@ -2014,7 +2016,7 @@
       </c>
       <c r="I26" s="14"/>
     </row>
-    <row r="27" spans="2:13" ht="15.75">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B27" s="18" t="s">
         <v>51</v>
       </c>
@@ -2036,7 +2038,7 @@
       </c>
       <c r="I27" s="14"/>
     </row>
-    <row r="28" spans="2:13" ht="15.75">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B28" s="18"/>
       <c r="C28" s="8" t="s">
         <v>54</v>
@@ -2058,7 +2060,7 @@
       </c>
       <c r="I28" s="14"/>
     </row>
-    <row r="29" spans="2:13" ht="15.75">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B29" s="18"/>
       <c r="C29" s="8" t="s">
         <v>56</v>
@@ -2081,7 +2083,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="2:13" ht="15.75">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B30" s="18"/>
       <c r="C30" s="8" t="s">
         <v>59</v>
@@ -2103,7 +2105,7 @@
       </c>
       <c r="I30" s="14"/>
     </row>
-    <row r="31" spans="2:13" ht="15.75">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B31" s="18"/>
       <c r="C31" s="8" t="s">
         <v>60</v>
@@ -2123,7 +2125,7 @@
       </c>
       <c r="I31" s="14"/>
     </row>
-    <row r="32" spans="2:13" ht="15.75">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B32" s="18"/>
       <c r="C32" s="8" t="s">
         <v>62</v>
@@ -2145,7 +2147,7 @@
       </c>
       <c r="I32" s="14"/>
     </row>
-    <row r="33" spans="2:9" ht="15.75">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B33" s="18"/>
       <c r="C33" s="23" t="s">
         <v>63</v>
@@ -2165,7 +2167,7 @@
       </c>
       <c r="I33" s="14"/>
     </row>
-    <row r="34" spans="2:9" ht="15.75">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B34" s="18"/>
       <c r="C34" s="8" t="s">
         <v>64</v>
@@ -2187,7 +2189,7 @@
       </c>
       <c r="I34" s="14"/>
     </row>
-    <row r="35" spans="2:9" ht="15.75">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B35" s="18"/>
       <c r="C35" s="8" t="s">
         <v>59</v>
@@ -2209,7 +2211,7 @@
       </c>
       <c r="I35" s="14"/>
     </row>
-    <row r="36" spans="2:9" ht="15.75">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B36" s="18"/>
       <c r="C36" s="23" t="s">
         <v>65</v>
@@ -2229,7 +2231,7 @@
       </c>
       <c r="I36" s="14"/>
     </row>
-    <row r="37" spans="2:9" ht="15.75">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B37" s="18"/>
       <c r="C37" s="8" t="s">
         <v>59</v>
@@ -2251,7 +2253,7 @@
       </c>
       <c r="I37" s="14"/>
     </row>
-    <row r="38" spans="2:9" ht="15.75">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B38" s="18"/>
       <c r="C38" s="8" t="s">
         <v>66</v>
@@ -2273,7 +2275,7 @@
       </c>
       <c r="I38" s="14"/>
     </row>
-    <row r="39" spans="2:9" ht="15.75">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B39" s="18"/>
       <c r="C39" s="8" t="s">
         <v>67</v>
@@ -2295,7 +2297,7 @@
       </c>
       <c r="I39" s="14"/>
     </row>
-    <row r="40" spans="2:9" ht="15.75">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B40" s="18"/>
       <c r="C40" s="8" t="s">
         <v>68</v>
@@ -2315,7 +2317,7 @@
       </c>
       <c r="I40" s="14"/>
     </row>
-    <row r="41" spans="2:9" ht="15.75">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B41" s="18"/>
       <c r="C41" s="8" t="s">
         <v>56</v>
@@ -2335,7 +2337,7 @@
       </c>
       <c r="I41" s="14"/>
     </row>
-    <row r="42" spans="2:9" ht="15.75">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B42" s="18"/>
       <c r="C42" s="23" t="s">
         <v>69</v>
@@ -2347,7 +2349,7 @@
       <c r="H42" s="9"/>
       <c r="I42" s="15"/>
     </row>
-    <row r="43" spans="2:9" ht="15.75">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B43" s="18"/>
       <c r="C43" s="8" t="s">
         <v>70</v>
@@ -2367,7 +2369,7 @@
       </c>
       <c r="I43" s="14"/>
     </row>
-    <row r="44" spans="2:9" ht="15.75">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B44" s="18"/>
       <c r="C44" s="8" t="s">
         <v>71</v>
@@ -2389,7 +2391,7 @@
       </c>
       <c r="I44" s="14"/>
     </row>
-    <row r="45" spans="2:9" ht="15.75">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B45" s="18"/>
       <c r="C45" s="8" t="s">
         <v>72</v>
@@ -2411,7 +2413,7 @@
       </c>
       <c r="I45" s="14"/>
     </row>
-    <row r="46" spans="2:9" ht="15.75">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B46" s="18"/>
       <c r="C46" s="8" t="s">
         <v>73</v>
@@ -2433,7 +2435,7 @@
       </c>
       <c r="I46" s="14"/>
     </row>
-    <row r="47" spans="2:9" ht="15.75">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B47" s="18"/>
       <c r="C47" s="8" t="s">
         <v>74</v>
@@ -2455,7 +2457,7 @@
       </c>
       <c r="I47" s="14"/>
     </row>
-    <row r="48" spans="2:9" ht="15.75">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B48" s="21" t="s">
         <v>75</v>
       </c>
@@ -2479,7 +2481,7 @@
       </c>
       <c r="I48" s="14"/>
     </row>
-    <row r="49" spans="2:11" ht="15.75">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B49" s="21"/>
       <c r="C49" s="8" t="s">
         <v>78</v>
@@ -2501,7 +2503,7 @@
       </c>
       <c r="I49" s="14"/>
     </row>
-    <row r="50" spans="2:11" ht="15.75">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B50" s="21"/>
       <c r="C50" s="8" t="s">
         <v>79</v>
@@ -2521,7 +2523,7 @@
       </c>
       <c r="I50" s="14"/>
     </row>
-    <row r="51" spans="2:11" ht="15.75">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B51" s="21"/>
       <c r="C51" s="8" t="s">
         <v>80</v>
@@ -2541,7 +2543,7 @@
       </c>
       <c r="I51" s="14"/>
     </row>
-    <row r="52" spans="2:11" ht="15.75">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B52" s="21"/>
       <c r="C52" s="8" t="s">
         <v>81</v>
@@ -2561,7 +2563,7 @@
       </c>
       <c r="I52" s="14"/>
     </row>
-    <row r="53" spans="2:11" ht="15.75">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B53" s="21"/>
       <c r="C53" s="8" t="s">
         <v>82</v>
@@ -2581,7 +2583,7 @@
       </c>
       <c r="I53" s="14"/>
     </row>
-    <row r="54" spans="2:11" ht="15.75">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B54" s="21"/>
       <c r="C54" s="8" t="s">
         <v>83</v>
@@ -2601,7 +2603,7 @@
       </c>
       <c r="I54" s="14"/>
     </row>
-    <row r="55" spans="2:11" ht="15.75">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B55" s="21"/>
       <c r="C55" s="8" t="s">
         <v>84</v>
@@ -2623,7 +2625,7 @@
       </c>
       <c r="I55" s="14"/>
     </row>
-    <row r="56" spans="2:11" ht="15.75">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B56" s="13" t="s">
         <v>85</v>
       </c>
@@ -2645,7 +2647,7 @@
       </c>
       <c r="I56" s="15"/>
     </row>
-    <row r="57" spans="2:11" ht="15.75">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B57" s="13"/>
       <c r="C57" s="9" t="s">
         <v>87</v>
@@ -2665,10 +2667,10 @@
       </c>
       <c r="I57" s="15"/>
     </row>
-    <row r="58" spans="2:11" ht="15.75">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B58" s="24"/>
       <c r="C58" s="19" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D58" s="19">
         <v>2</v>
@@ -2680,26 +2682,18 @@
         <v>2</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="H58" s="19" t="s">
         <v>14</v>
       </c>
       <c r="I58" s="20"/>
     </row>
-    <row r="59" spans="2:11" ht="15.75"/>
-    <row r="60" spans="2:11" ht="15.75"/>
-    <row r="61" spans="2:11" ht="15.75">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.4">
       <c r="K61" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11" ht="15.75"/>
-    <row r="63" spans="2:11" ht="15.75"/>
-    <row r="64" spans="2:11" ht="15.75"/>
-    <row r="65" ht="15.75"/>
-    <row r="66" ht="15.75"/>
-    <row r="68" ht="15.75"/>
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2709,35 +2703,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC87651-CAE3-434B-AE6A-BF668D200E5B}">
   <dimension ref="C2:M19"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="3:13">
+    <row r="2" spans="3:13" x14ac:dyDescent="0.4">
       <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="3:13" x14ac:dyDescent="0.4">
+      <c r="D4" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="4" spans="3:13">
-      <c r="D4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>97</v>
-      </c>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" spans="3:13">
+    <row r="5" spans="3:13" x14ac:dyDescent="0.4">
       <c r="D5" s="30"/>
       <c r="E5" s="7">
         <v>1</v>
@@ -2758,7 +2752,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="3:13">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.4">
       <c r="D6" s="32">
         <v>7</v>
       </c>
@@ -2781,7 +2775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="3:13">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.4">
       <c r="D7" s="32">
         <v>14</v>
       </c>
@@ -2804,7 +2798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="3:13">
+    <row r="8" spans="3:13" x14ac:dyDescent="0.4">
       <c r="D8" s="35">
         <v>21</v>
       </c>
@@ -2827,7 +2821,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="3:13">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.4">
       <c r="D9" s="36">
         <v>28</v>
       </c>
@@ -2842,9 +2836,9 @@
       <c r="I9" s="39"/>
       <c r="J9" s="40"/>
     </row>
-    <row r="12" spans="3:13">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.4">
       <c r="D12" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2861,7 +2855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="3:13">
+    <row r="13" spans="3:13" x14ac:dyDescent="0.4">
       <c r="D13" s="4">
         <v>5</v>
       </c>
@@ -2884,7 +2878,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="3:13">
+    <row r="14" spans="3:13" x14ac:dyDescent="0.4">
       <c r="D14" s="2">
         <v>12</v>
       </c>
@@ -2907,7 +2901,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="3:13">
+    <row r="15" spans="3:13" x14ac:dyDescent="0.4">
       <c r="D15" s="41">
         <v>19</v>
       </c>
@@ -2934,7 +2928,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="3:13">
+    <row r="16" spans="3:13" x14ac:dyDescent="0.4">
       <c r="D16" s="1">
         <v>26</v>
       </c>
@@ -2959,30 +2953,46 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="12:13">
+    <row r="17" spans="12:13" x14ac:dyDescent="0.4">
       <c r="L17" s="45"/>
       <c r="M17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="12:13">
+    <row r="18" spans="12:13" x14ac:dyDescent="0.4">
       <c r="L18" s="46"/>
       <c r="M18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="19" spans="12:13">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="12:13" x14ac:dyDescent="0.4">
       <c r="L19" s="47"/>
       <c r="M19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100FA41B8A39F5D7C42A915EA3203D3475A" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7bd4a93b8f826dde0255a5a9c5b761a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9ec34610-451d-4630-b8fd-572cd48b9242" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a85badd7ad608573bfc58ade974ad5c" ns2:_="">
     <xsd:import namespace="9ec34610-451d-4630-b8fd-572cd48b9242"/>
@@ -3120,29 +3130,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88BF7853-01BD-4208-BBA6-30D8498DCFB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BDE39E9-6F33-46E7-B7AF-EFADD9F8D015}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEEB1B50-1D2F-4568-B87D-D265AEA518FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEEB1B50-1D2F-4568-B87D-D265AEA518FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BDE39E9-6F33-46E7-B7AF-EFADD9F8D015}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88BF7853-01BD-4208-BBA6-30D8498DCFB7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9ec34610-451d-4630-b8fd-572cd48b9242"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SprintUp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F442ABD6-F405-47C0-B82C-608641BE0EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F16197B-3C27-4AD4-B166-A40058BD3ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DE6BE46-6D40-408E-8663-EDE3F977B8C2}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6DE6BE46-6D40-408E-8663-EDE3F977B8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -473,16 +473,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>提出</t>
-    <rPh sb="0" eb="2">
-      <t>テイシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>登った距離計測</t>
     <rPh sb="5" eb="7">
       <t>ケイソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完全提出</t>
+    <rPh sb="0" eb="2">
+      <t>カンゼン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイシュツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2670,7 +2673,7 @@
     <row r="58" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B58" s="24"/>
       <c r="C58" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="19">
         <v>2</v>
@@ -2968,7 +2971,7 @@
     <row r="19" spans="12:13" x14ac:dyDescent="0.4">
       <c r="L19" s="47"/>
       <c r="M19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2978,21 +2981,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100FA41B8A39F5D7C42A915EA3203D3475A" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7bd4a93b8f826dde0255a5a9c5b761a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9ec34610-451d-4630-b8fd-572cd48b9242" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a85badd7ad608573bfc58ade974ad5c" ns2:_="">
     <xsd:import namespace="9ec34610-451d-4630-b8fd-572cd48b9242"/>
@@ -3130,24 +3118,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BDE39E9-6F33-46E7-B7AF-EFADD9F8D015}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEEB1B50-1D2F-4568-B87D-D265AEA518FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88BF7853-01BD-4208-BBA6-30D8498DCFB7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3163,4 +3149,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEEB1B50-1D2F-4568-B87D-D265AEA518FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BDE39E9-6F33-46E7-B7AF-EFADD9F8D015}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>